--- a/docs/sprint2/audit/audit-Novosolova.xlsx
+++ b/docs/sprint2/audit/audit-Novosolova.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +27,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -59,16 +48,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
@@ -77,10 +66,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -448,16 +437,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,20 +468,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Критерій</t>
+          <t>Критерій (моя оцінка)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Опис дефекту (пункт чек-листа, цитата)</t>
+          <t>Пункт чек-листа</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Пропозиція виправлення</t>
+          <t>Що знайдено (запис під час перевірки)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Пропозиція (чернетка)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Результат зведення</t>
         </is>
@@ -505,12 +500,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>F-120</t>
+          <t>GUI-10</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -520,17 +515,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>п. 2: F-120 «додати товар до списку обраного … без входу в систему» суперечить GUI-40 (гостю — «Unauthorized…», товар не додається) і ролям 2.1 (обране — лише зареєстрованому покупцю).</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>F-120: «Зареєстрований покупець, який увійшов у систему, додає товар до списку обраного кнопкою «Add to favourites»; для гостя поведінку визначає GUI-40. Список обраного доступний у кабінеті («My favorites»), де позицію можна видалити».</t>
+          <t>У шапці є перемикач мови інтерфейсу, а в 2.2 сказано, що інтерфейс demo англійською.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 11 реєстру</t>
+          <t>Прибрати перемикач з GUI-10 або перелічити мови, які він має перемикати.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Відхилено на обговоренні (див. «Спірні»)</t>
         </is>
       </c>
     </row>
@@ -542,12 +542,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>F-40</t>
+          <t>GUI-20</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -557,17 +557,22 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>п. 2: F-40 «по 9 карток на сторінці» суперечить GUI-20 «по 12 карток на сторінці».</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>GUI-20: «Картки каталогу розміщуються сіткою у три колонки по 9 карток на сторінці (три ряди)…» — узгоджено з F-40 і поточною версією demo.</t>
+          <t>«по 12 карток на сторінці» — у F-40 9 карток. У demo теж 9.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 10 реєстру</t>
+          <t>GUI-20: 9 карток (3 колонки × 3 ряди).</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 10 реєстру (у реєстрі під ID F-40)</t>
         </is>
       </c>
     </row>
@@ -579,7 +584,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GUI-10</t>
+          <t>GUI-40</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -594,17 +599,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Перемикач мови інтерфейсу при тому, що 2.2 фіксує інтерфейс demo англійською.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Прибрати перемикач або описати перелік мов.</t>
+          <t>Гість натискає «Add to favourites» → «Unauthorized…», товар не додається. А F-120 каже, що додати можна без входу. Плюс у 2.1 обране є тільки в зареєстрованого покупця.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Відхилено на обговоренні (див. «Спірні»)</t>
+          <t>Виправити F-120: обране — лише після входу.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 11 реєстру (у реєстрі під ID F-120)</t>
         </is>
       </c>
     </row>
@@ -616,7 +626,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>GUI-100</t>
+          <t>GUI-50</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -626,22 +636,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Тестопридатність</t>
+          <t>Однозначність</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>«Кольорова схема … приємною і сучасною, а шрифти — легкими для читання» — суб'єктивні оцінки, спостережуваного критерію немає.</t>
+          <t>п. 4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>«Основний текст на всіх сторінках — шрифтом не менше 14 px; контраст тексту до фону — не менше 4,5:1 (WCAG 2.1, рівень AA); перевірка — Lighthouse або axe DevTools».</t>
+          <t>Повідомлення про помилку «біля поля або у верхній частині форми» — два різні місця.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 23 реєстру</t>
+          <t>Вибрати одне: під полем.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 3 реєстру</t>
         </is>
       </c>
     </row>
@@ -653,7 +668,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>GUI-50</t>
+          <t>GUI-60</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -663,22 +678,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Однозначність</t>
+          <t>Простежуваність</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>п. 4: «відображається біля відповідного поля або у верхній частині форми» — два допустимі місця, тест має два очікувані результати.</t>
+          <t>п. 1, 2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>«Повідомлення про помилку валідації відображається текстом безпосередньо під відповідним полем; форма з помилками не надсилається, введені дані у полях зберігаються».</t>
+          <t>Ідентифікатор GUI-60 у двох вимогах (вхід і реєстрація).</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 3 реєстру</t>
+          <t>Формі реєстрації — інший вільний ID.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 14 реєстру</t>
         </is>
       </c>
     </row>
@@ -690,7 +710,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GUI-60 (форма реєстрації)</t>
+          <t>GUI-80</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -700,22 +720,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Простежуваність</t>
+          <t>Здійсненність</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>п. 1, 2: ідентифікатор GUI-60 присвоєно двом різним вимогам — формі входу і формі реєстрації; посилання «GUI-60» неоднозначне.</t>
+          <t>єдиний пункт</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Форма входу лишається GUI-60; формі реєстрації присвоєно вільний проміжний ID GUI-65.</t>
+          <t>7680×4320 без стиснення і 50 мс «за будь-якого з'єднання» — так не буває.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 14 реєстру</t>
+          <t>Зменшити вимоги до зображень, дозволити JPEG/WebP.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 19 реєстру; виправлення доопрацьовано при зведенні</t>
         </is>
       </c>
     </row>
@@ -727,7 +752,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>GUI-80</t>
+          <t>GUI-100</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -737,22 +762,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Здійсненність</t>
+          <t>Тестопридатність</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>«не менше 8K (7680×4320) без стиснення … не довше ніж за 50 мс кожне за будь-якого з'єднання» — нестиснене 8K-зображення ≈ 100 МБ, за 50 мс фізично недосяжно навіть на гігабітному каналі.</t>
+          <t>практичний тест</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>«Зображення на картках каталогу — не менше 400×400 пікселів, на сторінці товару — не менше 1000×1000 пікселів, формат JPEG або WebP; за з'єднання 10 Мбіт/с зображення сторінки товару завантажується не довше ніж за 1 с» (потребує підтвердження замовником).</t>
+          <t>«приємною і сучасною» — як це перевірити?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 19 реєстру</t>
+          <t>Розмір шрифту від 14 px, контраст тексту 4,5:1.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 23 реєстру</t>
         </is>
       </c>
     </row>
@@ -764,7 +794,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -774,22 +804,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Повнота</t>
+          <t>Тестопридатність</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>п. 3: посилання на «Регламент програми лояльності ШопЛайн-ЛП-2025», розділ 4 — документ не входить до переліку 1.4 і команді не переданий.</t>
+          <t>практичний тест</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>«…розділ про програму лояльності описує правила знижки за обсяг, вартості доставки і промокодів відповідно до вимог BL-50 … BL-80 цієї специфікації».</t>
+          <t>«за будь-якого з'єднання і на будь-якому пристрої» — такі умови не відтворити, тест не напишеш.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 8 реєстру</t>
+          <t>Зафіксувати умови вимірювання (Chrome на ПК, 10 Мбіт/с) і реальний час (3 с?).</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 21 реєстру; при зведенні перекласифіковано у здійсненність (див. «Спірні»)</t>
         </is>
       </c>
     </row>
@@ -801,7 +836,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -811,22 +846,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Здійсненність</t>
+          <t>Тестопридатність</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>«не довше ніж за 0,1 с за будь-якого з'єднання з Інтернетом і на будь-якому пристрої» — недосяжно для повільних з'єднань (2G, супутник) і слабких пристроїв.</t>
+          <t>практичний тест, слова-маркери</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>«У Chrome 120+ на ПК за з'єднання 10 Мбіт/с із затримкою до 50 мс сторінка каталогу повністю завантажується (подія load) не довше ніж за 3 с; медіана з 10 вимірювань у DevTools/Lighthouse».</t>
+          <t>«надійно захищені», «не містить вразливостей» — відсутність усіх вразливостей довести неможливо.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 21 реєстру</t>
+          <t>Замінити на конкретні перевірки: HTTPS, хеш паролів, 401/403 в API, ZAP-сканування.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 24 реєстру</t>
         </is>
       </c>
     </row>
@@ -838,7 +878,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>U-10</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -853,17 +893,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>«Дані покупців надійно захищені, а система не містить вразливостей» — класична неперевірювана вимога: відсутність усіх вразливостей довести неможливо.</t>
+          <t>практичний тест, слова-маркери</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>«Обмін даними — лише HTTPS; паролі зберігаються тільки у вигляді хешу (bcrypt або Argon2); API кабінету й рахунків-інвойсів повертає 401 без токена і 403 на запит даних іншого покупця; сканування OWASP ZAP (baseline) не виявляє вразливостей рівня High».</t>
+          <t>«інтуїтивно зрозумілим і зручним» — маркери, критерію немає.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 24 реєстру</t>
+          <t>Юзабіліті-перевірка на 5 учасниках: замовлення за ≤ 5 хв.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 25 реєстру</t>
         </is>
       </c>
     </row>
@@ -875,7 +920,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-10</t>
+          <t>розд. 6, рядок після U-20, без ID</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -885,22 +930,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Тестопридатність</t>
+          <t>Простежуваність</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>«Інтерфейс є інтуїтивно зрозумілим і зручним для всіх категорій користувачів» — слова-маркери «інтуїтивно», «зручно», критерію немає.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>«Новий користувач без інструктажу знаходить товар пошуком і оформлює замовлення не довше ніж за 5 хв і не більше ніж з однією помилкою; перевірка на 5 учасниках, критерій — 4 з 5».</t>
+          <t>Вимога «коректно відображається за ширини вікна 375 пікселів…» без ідентифікатора.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 25 реєстру</t>
+          <t>Дати наступний вільний ID — U-30.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 15 реєстру</t>
         </is>
       </c>
     </row>
@@ -912,7 +962,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>розд. 6, рядок після U-20, без ID</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -922,22 +972,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Простежуваність</t>
+          <t>Повнота</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>п. 2: вимога «Інтерфейс коректно відображається за ширини вікна 375 пікселів…» не має ідентифікатора.</t>
+          <t>п. 3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Присвоєно наступний вільний ID: U-30.</t>
+          <t>«згідно з «Регламентом програми лояльності ШопЛайн-ЛП-2025», розділ 4» — цього документа немає в 1.4, і нам його не передавали.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 15 реєстру</t>
+          <t>Посилатися на BL-50…BL-80 цієї SRS замість регламенту.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 8 реєстру</t>
         </is>
       </c>
     </row>
@@ -952,11 +1007,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1022,7 +1077,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Знайдено (всього)</t>
+          <t>Записів в аркуші</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1032,7 +1087,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Прийнято до реєстру</t>
+          <t>Прийнято до реєстру як окремий дефект</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1042,17 +1097,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Відхилено</t>
+          <t>Об'єднано з іншим записом при зведенні</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>— Однозначність</t>
+          <t>Відхилено на обговоренні</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1062,7 +1117,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>— Повнота</t>
+          <t>Перекласифіковано при зведенні</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1072,41 +1127,81 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>— Несуперечливість</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>3</v>
-      </c>
+          <t>Записи за критерієм (моя оцінка)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>— Простежуваність</t>
+          <t>— Однозначність</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>— Здійсненність</t>
+          <t>— Повнота</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>— Тестопридатність</t>
+          <t>— Несуперечливість</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>— Простежуваність</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>— Здійсненність</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>— Тестопридатність</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Примітка</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Колонки «Що знайдено» і «Пропозиція» — формулювання до зведення; узгоджений текст дефекту і виправлення — у requirements-defects.xlsx, аркуш «Реєстр».</t>
+        </is>
       </c>
     </row>
   </sheetData>
